--- a/InputData/plcy-schd/FT/Final Time.xlsx
+++ b/InputData/plcy-schd/FT/Final Time.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\plcy-schd\FT\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F9DE17-3F67-4670-A668-09134A9E35FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="27960" windowHeight="13875"/>
+    <workbookView xWindow="31770" yWindow="1185" windowWidth="23310" windowHeight="13380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -59,7 +65,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -97,13 +103,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -114,14 +119,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -159,7 +167,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -231,7 +239,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -404,7 +412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -431,36 +439,33 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-    </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -471,7 +476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -488,7 +493,7 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>2050</v>
+        <v>2070</v>
       </c>
     </row>
   </sheetData>
